--- a/data/excel/funders.xlsx
+++ b/data/excel/funders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vackovab\Documents\nr-taxonomies\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9D6D9D-B921-461A-A95E-FBD77596161B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC52A1F-238A-443D-A201-B60B6BDEBCDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nr" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="393">
   <si>
     <t>code</t>
   </si>
@@ -1201,6 +1201,12 @@
   </si>
   <si>
     <t>https://ror.org/03613d656</t>
+  </si>
+  <si>
+    <t>usi-funding</t>
+  </si>
+  <si>
+    <t>USI Institutional Research Fund at Università della Svizzera italiana</t>
   </si>
 </sst>
 </file>
@@ -1609,22 +1615,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N90"/>
-  <sheetFormatPr defaultColWidth="25.5703125" defaultRowHeight="15"/>
+  <dimension ref="A1:N92"/>
+  <sheetFormatPr defaultColWidth="25.5546875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" customWidth="1"/>
-    <col min="8" max="8" width="25.5703125" customWidth="1"/>
-    <col min="9" max="9" width="22.42578125" customWidth="1"/>
-    <col min="13" max="13" width="37.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5546875" customWidth="1"/>
+    <col min="6" max="6" width="25.109375" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" customWidth="1"/>
+    <col min="8" max="8" width="25.5546875" customWidth="1"/>
+    <col min="9" max="9" width="22.44140625" customWidth="1"/>
+    <col min="13" max="13" width="37.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75">
+    <row r="1" spans="1:14" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1644,7 +1650,7 @@
       <c r="K1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75">
+    <row r="2" spans="1:14" ht="15.6">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1664,7 +1670,7 @@
       <c r="K2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75">
+    <row r="3" spans="1:14" ht="15.6">
       <c r="A3" s="5"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1678,7 +1684,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="5"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75">
+    <row r="5" spans="1:14" ht="15.6">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1722,7 +1728,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75">
+    <row r="6" spans="1:14" ht="15.6">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1756,7 +1762,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15.75">
+    <row r="7" spans="1:14" ht="15.6">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1786,7 +1792,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75">
+    <row r="8" spans="1:14" ht="15.6">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1816,7 +1822,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.75">
+    <row r="9" spans="1:14" ht="15.6">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1848,7 +1854,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75">
+    <row r="10" spans="1:14" ht="15.6">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -1878,7 +1884,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15.75">
+    <row r="11" spans="1:14" ht="15.6">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1912,7 +1918,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75">
+    <row r="12" spans="1:14" ht="15.6">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1937,7 +1943,7 @@
       </c>
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75">
+    <row r="13" spans="1:14" ht="15.6">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -1962,7 +1968,7 @@
       </c>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75">
+    <row r="14" spans="1:14" ht="15.6">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -1987,7 +1993,7 @@
       </c>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75">
+    <row r="15" spans="1:14" ht="15.6">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -2012,7 +2018,7 @@
       </c>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75">
+    <row r="16" spans="1:14" ht="15.6">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -2037,7 +2043,7 @@
       </c>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75">
+    <row r="17" spans="1:14" ht="15.6">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -2062,7 +2068,7 @@
       </c>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="15.75">
+    <row r="18" spans="1:14" ht="15.6">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -2087,7 +2093,7 @@
       </c>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75">
+    <row r="19" spans="1:14" ht="15.6">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -2112,7 +2118,7 @@
       </c>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75">
+    <row r="20" spans="1:14" ht="15.6">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -2137,7 +2143,7 @@
       </c>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="15.75">
+    <row r="21" spans="1:14" ht="15.6">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -2162,7 +2168,7 @@
       </c>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75">
+    <row r="22" spans="1:14" ht="15.6">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -2187,7 +2193,7 @@
       </c>
       <c r="M22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75">
+    <row r="23" spans="1:14" ht="15.6">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -2212,7 +2218,7 @@
       </c>
       <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75">
+    <row r="24" spans="1:14" ht="15.6">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -2237,7 +2243,7 @@
       </c>
       <c r="M24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75">
+    <row r="25" spans="1:14" ht="15.6">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -2262,7 +2268,7 @@
       </c>
       <c r="M25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75">
+    <row r="26" spans="1:14" ht="15.6">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -2294,7 +2300,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15.75">
+    <row r="27" spans="1:14" ht="15.6">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -2324,7 +2330,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.75">
+    <row r="28" spans="1:14" ht="15.6">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -2356,7 +2362,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15.75">
+    <row r="29" spans="1:14" ht="15.6">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -2386,7 +2392,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15.75">
+    <row r="30" spans="1:14" ht="15.6">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -2418,7 +2424,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15.75">
+    <row r="31" spans="1:14" ht="15.6">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -2450,7 +2456,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15.75">
+    <row r="32" spans="1:14" ht="15.6">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -2482,7 +2488,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.75">
+    <row r="33" spans="1:14" ht="15.6">
       <c r="A33" s="1">
         <v>1</v>
       </c>
@@ -2512,7 +2518,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="15.75">
+    <row r="34" spans="1:14" ht="15.6">
       <c r="A34" s="1">
         <v>1</v>
       </c>
@@ -2544,7 +2550,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15.75">
+    <row r="35" spans="1:14" ht="15.6">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -2576,7 +2582,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="15.75">
+    <row r="36" spans="1:14" ht="15.6">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -2608,7 +2614,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="15.75">
+    <row r="37" spans="1:14" ht="15.6">
       <c r="A37" s="1">
         <v>1</v>
       </c>
@@ -2640,7 +2646,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="15.75">
+    <row r="38" spans="1:14" ht="15.6">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -2672,7 +2678,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="15.75">
+    <row r="39" spans="1:14" ht="15.6">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -2702,7 +2708,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.75">
+    <row r="40" spans="1:14" ht="15.6">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="15.75">
+    <row r="41" spans="1:14" ht="15.6">
       <c r="A41" s="1">
         <v>1</v>
       </c>
@@ -2756,7 +2762,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="15.75">
+    <row r="42" spans="1:14" ht="15.6">
       <c r="A42" s="1">
         <v>1</v>
       </c>
@@ -2785,7 +2791,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15.75">
+    <row r="43" spans="1:14" ht="15.6">
       <c r="A43" s="1">
         <v>1</v>
       </c>
@@ -2804,7 +2810,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="15.75">
+    <row r="44" spans="1:14" ht="15.6">
       <c r="A44" s="1">
         <v>1</v>
       </c>
@@ -2823,7 +2829,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15.75">
+    <row r="45" spans="1:14" ht="15.6">
       <c r="A45" s="1">
         <v>1</v>
       </c>
@@ -2844,7 +2850,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15.75">
+    <row r="46" spans="1:14" ht="15.6">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -2865,7 +2871,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15.75">
+    <row r="47" spans="1:14" ht="15.6">
       <c r="A47" s="4">
         <v>1</v>
       </c>
@@ -2892,7 +2898,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15.75">
+    <row r="48" spans="1:14" ht="15.6">
       <c r="A48" s="4">
         <v>1</v>
       </c>
@@ -2916,7 +2922,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15.75">
+    <row r="49" spans="1:14" ht="15.6">
       <c r="A49" s="4">
         <v>1</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="15.75">
+    <row r="50" spans="1:14" ht="15.6">
       <c r="A50" s="4">
         <v>1</v>
       </c>
@@ -2967,7 +2973,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="15.75">
+    <row r="51" spans="1:14" ht="15.6">
       <c r="A51" s="4">
         <v>1</v>
       </c>
@@ -2994,7 +3000,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="15.75">
+    <row r="52" spans="1:14" ht="15.6">
       <c r="A52" s="4">
         <v>1</v>
       </c>
@@ -3021,7 +3027,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15.75">
+    <row r="53" spans="1:14" ht="15.6">
       <c r="A53" s="4">
         <v>1</v>
       </c>
@@ -3045,7 +3051,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.75">
+    <row r="54" spans="1:14" ht="15.6">
       <c r="A54" s="4">
         <v>1</v>
       </c>
@@ -3062,7 +3068,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="15.75">
+    <row r="55" spans="1:14" ht="15.6">
       <c r="A55" s="4">
         <v>1</v>
       </c>
@@ -3079,7 +3085,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="15.75">
+    <row r="56" spans="1:14" ht="15.6">
       <c r="A56" s="4">
         <v>1</v>
       </c>
@@ -3097,7 +3103,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="15.75">
+    <row r="57" spans="1:14" ht="15.6">
       <c r="A57" s="4">
         <v>1</v>
       </c>
@@ -3117,7 +3123,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="15.75">
+    <row r="58" spans="1:14" ht="15.6">
       <c r="A58" s="4">
         <v>1</v>
       </c>
@@ -3140,7 +3146,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="15.75">
+    <row r="59" spans="1:14" ht="15.6">
       <c r="A59" s="4">
         <v>1</v>
       </c>
@@ -3166,7 +3172,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="15.75">
+    <row r="60" spans="1:14" ht="15.6">
       <c r="A60" s="4">
         <v>1</v>
       </c>
@@ -3192,7 +3198,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15.75">
+    <row r="61" spans="1:14" ht="15.6">
       <c r="A61" s="4">
         <v>1</v>
       </c>
@@ -3218,7 +3224,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="15.75">
+    <row r="62" spans="1:14" ht="15.6">
       <c r="A62" s="4">
         <v>1</v>
       </c>
@@ -3235,7 +3241,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="15.75">
+    <row r="63" spans="1:14" ht="15.6">
       <c r="A63" s="4">
         <v>1</v>
       </c>
@@ -3261,7 +3267,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15.75">
+    <row r="64" spans="1:14" ht="15.6">
       <c r="A64" s="4">
         <v>1</v>
       </c>
@@ -3284,7 +3290,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="15.75">
+    <row r="65" spans="1:14" ht="15.6">
       <c r="A65" s="4">
         <v>1</v>
       </c>
@@ -3301,7 +3307,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="15.75">
+    <row r="66" spans="1:14" ht="15.6">
       <c r="A66" s="4">
         <v>1</v>
       </c>
@@ -3327,7 +3333,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="15.75">
+    <row r="67" spans="1:14" ht="15.6">
       <c r="A67" s="4">
         <v>1</v>
       </c>
@@ -3347,7 +3353,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="15.75">
+    <row r="68" spans="1:14" ht="15.6">
       <c r="A68" s="4">
         <v>1</v>
       </c>
@@ -3370,7 +3376,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="15.75">
+    <row r="69" spans="1:14" ht="15.6">
       <c r="A69" s="4">
         <v>1</v>
       </c>
@@ -3393,7 +3399,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="15.75">
+    <row r="70" spans="1:14" ht="15.6">
       <c r="A70" s="4">
         <v>1</v>
       </c>
@@ -3407,7 +3413,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="15.75">
+    <row r="71" spans="1:14" ht="15.6">
       <c r="A71" s="4">
         <v>1</v>
       </c>
@@ -3431,7 +3437,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="15.75">
+    <row r="72" spans="1:14" ht="15.6">
       <c r="A72" s="4">
         <v>1</v>
       </c>
@@ -3457,7 +3463,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="15.75">
+    <row r="73" spans="1:14" ht="15.6">
       <c r="A73" s="4">
         <v>1</v>
       </c>
@@ -3477,7 +3483,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="15.75">
+    <row r="74" spans="1:14" ht="15.6">
       <c r="A74" s="4">
         <v>1</v>
       </c>
@@ -3504,7 +3510,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="15.75">
+    <row r="75" spans="1:14" ht="15.6">
       <c r="A75" s="4">
         <v>1</v>
       </c>
@@ -3527,7 +3533,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="15.75">
+    <row r="76" spans="1:14" ht="15.6">
       <c r="A76" s="4">
         <v>1</v>
       </c>
@@ -3553,7 +3559,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15.75">
+    <row r="77" spans="1:14" ht="15.6">
       <c r="A77" s="4">
         <v>1</v>
       </c>
@@ -3571,7 +3577,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="15.75">
+    <row r="78" spans="1:14" ht="15.6">
       <c r="A78" s="4">
         <v>1</v>
       </c>
@@ -3594,7 +3600,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="15.75">
+    <row r="79" spans="1:14" ht="15.6">
       <c r="A79" s="4">
         <v>1</v>
       </c>
@@ -3620,7 +3626,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="15.75">
+    <row r="80" spans="1:14" ht="15.6">
       <c r="A80" s="4">
         <v>1</v>
       </c>
@@ -3692,7 +3698,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="15.75">
+    <row r="83" spans="1:14" ht="15.6">
       <c r="A83" s="4">
         <v>1</v>
       </c>
@@ -3718,7 +3724,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="15.75">
+    <row r="84" spans="1:14" ht="15.6">
       <c r="A84" s="4">
         <v>1</v>
       </c>
@@ -3741,7 +3747,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="15.75">
+    <row r="85" spans="1:14" ht="15.6">
       <c r="A85" s="4">
         <v>1</v>
       </c>
@@ -3764,7 +3770,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="15.75">
+    <row r="86" spans="1:14" ht="15.6">
       <c r="A86" s="4">
         <v>1</v>
       </c>
@@ -3784,7 +3790,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="15.75">
+    <row r="87" spans="1:14" ht="15.6">
       <c r="A87" s="4">
         <v>1</v>
       </c>
@@ -3804,7 +3810,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="15.75">
+    <row r="88" spans="1:14" ht="15.6">
       <c r="A88" s="4">
         <v>1</v>
       </c>
@@ -3824,7 +3830,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="15.75">
+    <row r="89" spans="1:14" ht="15.6">
       <c r="A89" s="4">
         <v>1</v>
       </c>
@@ -3847,8 +3853,8 @@
         <v>385</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="15.75">
-      <c r="A90" s="14">
+    <row r="90" spans="1:14" ht="15.6">
+      <c r="A90" s="4">
         <v>1</v>
       </c>
       <c r="B90" t="s">
@@ -3872,6 +3878,23 @@
       <c r="N90" t="s">
         <v>390</v>
       </c>
+    </row>
+    <row r="91" spans="1:14" ht="15.6">
+      <c r="A91" s="14">
+        <v>1</v>
+      </c>
+      <c r="B91" t="s">
+        <v>391</v>
+      </c>
+      <c r="D91" t="s">
+        <v>392</v>
+      </c>
+      <c r="L91" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="15.6">
+      <c r="A92" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B80 B83:B1048576">
